--- a/VerveStacks_IND_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan60/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97D861F-4B18-4CF9-9376-ADD6F14A422F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814255A6-9D35-4010-9945-319C52DE0287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1498BC-47A6-403F-97B5-84974BB7C26F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39B648A-CC54-4E63-8EC3-53F113722380}">
   <dimension ref="B3:H54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6218,7 +6218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD2F15C-9702-4B9E-9E83-F11040289F4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1C7650-674A-4B61-92B2-3BA6C380EE0C}">
   <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7429,7 +7429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388207A4-8ABC-4E5B-A642-3D4A0FE44818}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464E0375-FBE0-4340-A8F1-3889575B574E}">
   <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan60/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan60/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814255A6-9D35-4010-9945-319C52DE0287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F056F6-5574-468E-99C8-96F4EDF1758C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39B648A-CC54-4E63-8EC3-53F113722380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51D8425-0184-4713-9E64-A5CCBA53100A}">
   <dimension ref="B3:H54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6218,7 +6218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1C7650-674A-4B61-92B2-3BA6C380EE0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5016B3B4-5F2C-4A2C-9CBF-904B5DE02884}">
   <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7429,7 +7429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464E0375-FBE0-4340-A8F1-3889575B574E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893E48AA-32F5-42AF-B13F-D509C832E3C6}">
   <dimension ref="B3:I49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
